--- a/xlsx/換色紀錄表(2411) 4號盤存.xlsx
+++ b/xlsx/換色紀錄表(2411) 4號盤存.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="8_{D2DBBC8B-7A72-EE46-B813-F1066388F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CEB69E-280A-EC44-907F-068C490E9A0F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{19850F94-3F21-044F-8D32-D0A812AA8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="庫存查詢表" sheetId="7" r:id="rId1"/>
@@ -3947,7 +3947,9 @@
     </row>
     <row r="5" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A5" s="125"/>
-      <c r="B5" s="121"/>
+      <c r="B5" s="121">
+        <v>45601</v>
+      </c>
       <c r="C5" s="27" t="s">
         <v>2</v>
       </c>
@@ -4064,7 +4066,9 @@
     </row>
     <row r="8" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A8" s="125"/>
-      <c r="B8" s="121"/>
+      <c r="B8" s="121">
+        <v>45603</v>
+      </c>
       <c r="C8" s="27" t="s">
         <v>2</v>
       </c>
@@ -4237,7 +4241,9 @@
     </row>
     <row r="13" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A13" s="125"/>
-      <c r="B13" s="121"/>
+      <c r="B13" s="121">
+        <v>45607</v>
+      </c>
       <c r="C13" s="27" t="s">
         <v>2</v>
       </c>
@@ -4272,7 +4278,9 @@
     </row>
     <row r="14" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A14" s="125"/>
-      <c r="B14" s="121"/>
+      <c r="B14" s="121">
+        <v>45607</v>
+      </c>
       <c r="C14" s="27" t="s">
         <v>24</v>
       </c>
@@ -4345,7 +4353,9 @@
     </row>
     <row r="16" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A16" s="125"/>
-      <c r="B16" s="121"/>
+      <c r="B16" s="121">
+        <v>45608</v>
+      </c>
       <c r="C16" s="27" t="s">
         <v>31</v>
       </c>
@@ -4427,7 +4437,9 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" s="125"/>
-      <c r="B18" s="121"/>
+      <c r="B18" s="121">
+        <v>45609</v>
+      </c>
       <c r="C18" s="27" t="s">
         <v>26</v>
       </c>
@@ -4466,7 +4478,9 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A19" s="125"/>
-      <c r="B19" s="121"/>
+      <c r="B19" s="121">
+        <v>45609</v>
+      </c>
       <c r="C19" s="27" t="s">
         <v>2</v>
       </c>
@@ -4503,7 +4517,9 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" s="125"/>
-      <c r="B20" s="121"/>
+      <c r="B20" s="121">
+        <v>45609</v>
+      </c>
       <c r="C20" s="27" t="s">
         <v>24</v>
       </c>
@@ -4575,7 +4591,9 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A22" s="125"/>
-      <c r="B22" s="121"/>
+      <c r="B22" s="121">
+        <v>45610</v>
+      </c>
       <c r="C22" s="27" t="s">
         <v>24</v>
       </c>
@@ -4610,7 +4628,9 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="125"/>
-      <c r="B23" s="121"/>
+      <c r="B23" s="121">
+        <v>45610</v>
+      </c>
       <c r="C23" s="27" t="s">
         <v>26</v>
       </c>
@@ -4647,7 +4667,9 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A24" s="125"/>
-      <c r="B24" s="121"/>
+      <c r="B24" s="121">
+        <v>45610</v>
+      </c>
       <c r="C24" s="27" t="s">
         <v>31</v>
       </c>
@@ -4717,7 +4739,9 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" s="125"/>
-      <c r="B26" s="121"/>
+      <c r="B26" s="121">
+        <v>45611</v>
+      </c>
       <c r="C26" s="27" t="s">
         <v>33</v>
       </c>
@@ -4754,7 +4778,9 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A27" s="125"/>
-      <c r="B27" s="121"/>
+      <c r="B27" s="121">
+        <v>45611</v>
+      </c>
       <c r="C27" s="27" t="s">
         <v>34</v>
       </c>
@@ -4791,7 +4817,9 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="125"/>
-      <c r="B28" s="121"/>
+      <c r="B28" s="121">
+        <v>45611</v>
+      </c>
       <c r="C28" s="27" t="s">
         <v>35</v>
       </c>
@@ -4865,7 +4893,9 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" s="125"/>
-      <c r="B30" s="121"/>
+      <c r="B30" s="121">
+        <v>45614</v>
+      </c>
       <c r="C30" s="27" t="s">
         <v>26</v>
       </c>
@@ -4941,7 +4971,9 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="125"/>
-      <c r="B32" s="121"/>
+      <c r="B32" s="121">
+        <v>45615</v>
+      </c>
       <c r="C32" s="27" t="s">
         <v>33</v>
       </c>
@@ -4978,7 +5010,9 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" s="125"/>
-      <c r="B33" s="121"/>
+      <c r="B33" s="121">
+        <v>45615</v>
+      </c>
       <c r="C33" s="27" t="s">
         <v>26</v>
       </c>
@@ -5097,7 +5131,9 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="125"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="121">
+        <v>45617</v>
+      </c>
       <c r="C36" s="27" t="s">
         <v>31</v>
       </c>
@@ -5177,7 +5213,9 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" s="125"/>
-      <c r="B38" s="121"/>
+      <c r="B38" s="121">
+        <v>45618</v>
+      </c>
       <c r="C38" s="27" t="s">
         <v>26</v>
       </c>
@@ -5323,7 +5361,9 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" s="125"/>
-      <c r="B42" s="121"/>
+      <c r="B42" s="121">
+        <v>45621</v>
+      </c>
       <c r="C42" s="27" t="s">
         <v>37</v>
       </c>
@@ -5362,7 +5402,9 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A43" s="125"/>
-      <c r="B43" s="121"/>
+      <c r="B43" s="121">
+        <v>45621</v>
+      </c>
       <c r="C43" s="27" t="s">
         <v>26</v>
       </c>
@@ -5444,7 +5486,9 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="125"/>
-      <c r="B45" s="158"/>
+      <c r="B45" s="121">
+        <v>45622</v>
+      </c>
       <c r="C45" s="153" t="s">
         <v>26</v>
       </c>
@@ -5485,7 +5529,9 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="125"/>
-      <c r="B46" s="158"/>
+      <c r="B46" s="121">
+        <v>45622</v>
+      </c>
       <c r="C46" s="153" t="s">
         <v>34</v>
       </c>
@@ -5525,7 +5571,9 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A47" s="125"/>
-      <c r="B47" s="158"/>
+      <c r="B47" s="121">
+        <v>45622</v>
+      </c>
       <c r="C47" s="153" t="s">
         <v>31</v>
       </c>
@@ -5607,7 +5655,9 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" s="125"/>
-      <c r="B49" s="158"/>
+      <c r="B49" s="158">
+        <v>45623</v>
+      </c>
       <c r="C49" s="153" t="s">
         <v>38</v>
       </c>
@@ -5644,7 +5694,9 @@
     </row>
     <row r="50" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="125"/>
-      <c r="B50" s="121"/>
+      <c r="B50" s="158">
+        <v>45623</v>
+      </c>
       <c r="C50" s="157" t="s">
         <v>33</v>
       </c>
@@ -5683,7 +5735,9 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A51" s="125"/>
-      <c r="B51" s="121"/>
+      <c r="B51" s="158">
+        <v>45623</v>
+      </c>
       <c r="C51" s="27" t="s">
         <v>26</v>
       </c>
@@ -5845,7 +5899,9 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" s="125"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="121">
+        <v>45625</v>
+      </c>
       <c r="C55" s="27" t="s">
         <v>26</v>
       </c>
@@ -7369,7 +7425,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45755</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
